--- a/REF.xlsx
+++ b/REF.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mengc\Documents\Claude\Projects\SALT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B03CB1E-E1BF-4608-8764-C023741FECB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DCE2295-61CF-43BE-BC12-CDCF8D2C564F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4920" yWindow="3195" windowWidth="28800" windowHeight="15345" xr2:uid="{61151892-9F39-475D-B6D6-5FE86B4D1897}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{61151892-9F39-475D-B6D6-5FE86B4D1897}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -326,10 +326,10 @@
     <t>安和昴</t>
   </si>
   <si>
-    <t>古关忧/平泽唯</t>
-  </si>
-  <si>
     <t>图片</t>
+  </si>
+  <si>
+    <t>平泽唯</t>
   </si>
 </sst>
 </file>
@@ -749,7 +749,7 @@
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G3" s="1"/>
     </row>
@@ -1030,7 +1030,7 @@
         <v>64</v>
       </c>
       <c r="D18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>65</v>
